--- a/output/topology_excel/9526.xlsx
+++ b/output/topology_excel/9526.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,18 +652,18 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,15 +718,15 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
         <v>20</v>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="F22" t="n">
         <v>13</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,40 +938,40 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>64</v>
+      </c>
+      <c r="F24" t="n">
         <v>29</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Door</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>148</v>
-      </c>
-      <c r="F24" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B25" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="F25" t="n">
         <v>13</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,54 +1048,54 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>235</v>
+        <v>412</v>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>772</v>
+        <v>124</v>
       </c>
       <c r="F32" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="F33" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>186</v>
+        <v>360</v>
       </c>
       <c r="F34" t="n">
         <v>29</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>861</v>
+        <v>47</v>
       </c>
       <c r="F35" t="n">
-        <v>293</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -1213,7 +1213,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="F36" t="n">
-        <v>132</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -1235,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="F37" t="n">
-        <v>200</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -1257,7 +1257,7 @@
         <v>3</v>
       </c>
       <c r="B38" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="F38" t="n">
-        <v>61</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>979</v>
+        <v>459</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>250</v>
+        <v>979</v>
       </c>
       <c r="F40" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="F41" t="n">
         <v>16</v>
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>250</v>
+        <v>98</v>
       </c>
       <c r="F42" t="n">
-        <v>147</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="F43" t="n">
-        <v>155</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F45" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B46" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="F46" t="n">
-        <v>31</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B47" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>435</v>
+        <v>186</v>
       </c>
       <c r="F47" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B48" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,18 +1488,18 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>287</v>
+        <v>176</v>
       </c>
       <c r="F48" t="n">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>405</v>
+        <v>176</v>
       </c>
       <c r="F49" t="n">
-        <v>204</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>186</v>
+        <v>421</v>
       </c>
       <c r="F50" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B51" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>345</v>
+        <v>233</v>
       </c>
       <c r="F51" t="n">
-        <v>145</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B52" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B53" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>374</v>
+        <v>62</v>
       </c>
       <c r="F53" t="n">
         <v>14</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>254</v>
+        <v>186</v>
       </c>
       <c r="F54" t="n">
         <v>13</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,18 +1642,18 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B56" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,18 +1664,18 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="F56" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B57" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,18 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="F57" t="n">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B58" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,18 +1708,18 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>250</v>
       </c>
       <c r="F58" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B59" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,18 +1730,18 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="F59" t="n">
-        <v>115</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B60" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>139</v>
+        <v>287</v>
       </c>
       <c r="F60" t="n">
-        <v>13</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,18 +1774,18 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="F61" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B62" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>421</v>
+        <v>109</v>
       </c>
       <c r="F62" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B63" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>253</v>
+        <v>106</v>
       </c>
       <c r="F63" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64">
@@ -1829,7 +1829,7 @@
         <v>21</v>
       </c>
       <c r="B64" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,18 +1840,18 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>556</v>
+        <v>110</v>
       </c>
       <c r="F64" t="n">
-        <v>281</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B65" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,18 +1862,18 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>176</v>
+        <v>435</v>
       </c>
       <c r="F65" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B66" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,18 +1884,18 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>112</v>
+        <v>298</v>
       </c>
       <c r="F66" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B67" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1906,18 +1906,18 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>40</v>
+        <v>374</v>
       </c>
       <c r="F67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B68" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>85</v>
+        <v>254</v>
       </c>
       <c r="F68" t="n">
         <v>13</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,18 +1950,18 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>261</v>
+        <v>115</v>
       </c>
       <c r="F69" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B70" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1972,18 +1972,18 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>177</v>
+        <v>261</v>
       </c>
       <c r="F70" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B71" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1994,15 +1994,15 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>245</v>
+        <v>87</v>
       </c>
       <c r="F71" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B72" t="n">
         <v>31</v>
@@ -2016,32 +2016,296 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="F72" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
+        <v>26</v>
+      </c>
+      <c r="B73" t="n">
+        <v>33</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>139</v>
+      </c>
+      <c r="F73" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>26</v>
+      </c>
+      <c r="B74" t="n">
+        <v>34</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>285</v>
+      </c>
+      <c r="F74" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>26</v>
+      </c>
+      <c r="B75" t="n">
+        <v>35</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>253</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>27</v>
+      </c>
+      <c r="B76" t="n">
+        <v>28</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>556</v>
+      </c>
+      <c r="F76" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>30</v>
+      </c>
+      <c r="B77" t="n">
         <v>31</v>
       </c>
-      <c r="B73" t="n">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>112</v>
+      </c>
+      <c r="F77" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>30</v>
+      </c>
+      <c r="B78" t="n">
         <v>32</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>233</v>
-      </c>
-      <c r="F73" t="n">
-        <v>25</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>40</v>
+      </c>
+      <c r="F78" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>30</v>
+      </c>
+      <c r="B79" t="n">
+        <v>33</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>85</v>
+      </c>
+      <c r="F79" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>31</v>
+      </c>
+      <c r="B80" t="n">
+        <v>33</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>261</v>
+      </c>
+      <c r="F80" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>32</v>
+      </c>
+      <c r="B81" t="n">
+        <v>33</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>177</v>
+      </c>
+      <c r="F81" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>33</v>
+      </c>
+      <c r="B82" t="n">
+        <v>34</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>245</v>
+      </c>
+      <c r="F82" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>329</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>12</v>
+      </c>
+      <c r="B84" t="n">
+        <v>18</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>219</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>13</v>
+      </c>
+      <c r="B85" t="n">
+        <v>22</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>96</v>
+      </c>
+      <c r="F85" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
